--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20261022.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20261022.xlsx
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>300,000</t>
+          <t>350,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>350,000</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>上銀</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -1525,12 +1525,12 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -1547,12 +1547,12 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -1569,12 +1569,12 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -1591,12 +1591,12 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -1613,12 +1613,12 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -1635,12 +1635,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>上銀</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
